--- a/src/main/resources/template/VulnerabilityReport.xlsx
+++ b/src/main/resources/template/VulnerabilityReport.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\osc\fosslight\data\template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20340" windowHeight="7710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20340" windowHeight="7716"/>
   </bookViews>
   <sheets>
-    <sheet name="CVE Info" sheetId="21" r:id="rId1"/>
+    <sheet name="Vulnerability Info" sheetId="21" r:id="rId1"/>
     <sheet name=".Data" sheetId="20" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'.Data'!$A$1:$A$163</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -23,13 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="283">
-  <si>
-    <t>OSS Name</t>
-  </si>
-  <si>
-    <t>OSS Version</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="282">
   <si>
     <t>License</t>
   </si>
@@ -884,30 +883,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CVE ID</t>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Published Date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Last Revised</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CVSS Score</t>
+    <t>Vulnerability Info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Source</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Component(name)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Severity(score)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Affected versions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modified Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1324,57 +1328,51 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="89.125" customWidth="1"/>
-    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.69921875" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" customWidth="1"/>
+    <col min="3" max="3" width="25.69921875" customWidth="1"/>
+    <col min="4" max="4" width="40.69921875" customWidth="1"/>
+    <col min="5" max="6" width="20.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>278</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>279</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G1" s="4" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1384,1213 +1382,1213 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E179"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="67" style="2" customWidth="1"/>
-    <col min="2" max="2" width="41.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.69921875" style="2" customWidth="1"/>
     <col min="3" max="4" width="34.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="45.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C31" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A70" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A71" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A72" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A74" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A76" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A77" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A78" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A114" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A118" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A119" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A122" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A126" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A127" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A128" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A134" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A137" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A138" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A141" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A145" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A146" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A147" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A148" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A153" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A154" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A155" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A156" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A158" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A159" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A160" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A161" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A168" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A173" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A175" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A178" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="3" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A179" s="2" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="2" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>
